--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="439" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E38A1391-AC83-4B2D-BEAB-C16FBC2DAA58}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62BE6B4F-357C-433B-A4EB-A5CACFFA7FD4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="223">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -230,9 +230,6 @@
     <t>Maradona</t>
   </si>
   <si>
-    <t>@pietro_actis</t>
-  </si>
-  <si>
     <t>@fabri1010</t>
   </si>
   <si>
@@ -257,15 +254,9 @@
     <t>@KAIROS_Burn17</t>
   </si>
   <si>
-    <t>@Mattia230</t>
-  </si>
-  <si>
     <t>Tristaban</t>
   </si>
   <si>
-    <t>XxMattiaxX</t>
-  </si>
-  <si>
     <t>@begghich</t>
   </si>
   <si>
@@ -278,9 +269,6 @@
     <t>ＡＲ♠️ｓｐｅｚｉａ</t>
   </si>
   <si>
-    <t>Sønサル•D•Lůffy</t>
-  </si>
-  <si>
     <t>ＡＲ❤️ＳＵＭＡＴＲＡ</t>
   </si>
   <si>
@@ -299,9 +287,6 @@
     <t>bughy</t>
   </si>
   <si>
-    <t>ＡＲ♠️ＢＡＣ</t>
-  </si>
-  <si>
     <t>Kekko03</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>vinz</t>
   </si>
   <si>
-    <t>shinigami</t>
-  </si>
-  <si>
     <t>aleman(statale)</t>
   </si>
   <si>
@@ -368,9 +350,6 @@
     <t>@speziaaa</t>
   </si>
   <si>
-    <t>@wa1n8</t>
-  </si>
-  <si>
     <t>@Sas0800</t>
   </si>
   <si>
@@ -389,9 +368,6 @@
     <t>@ArBughy</t>
   </si>
   <si>
-    <t>@BACWasTaken</t>
-  </si>
-  <si>
     <t>@K3kk07</t>
   </si>
   <si>
@@ -521,9 +497,6 @@
     <t>Frittu</t>
   </si>
   <si>
-    <t>Just_Dodo</t>
-  </si>
-  <si>
     <t>-roger8-</t>
   </si>
   <si>
@@ -539,12 +512,6 @@
     <t>tiau</t>
   </si>
   <si>
-    <t>two ciamela</t>
-  </si>
-  <si>
-    <t>Uchiha Madara</t>
-  </si>
-  <si>
     <t>@luca3689</t>
   </si>
   <si>
@@ -605,9 +572,6 @@
     <t>@Frittuuu</t>
   </si>
   <si>
-    <t>@edoogrigo</t>
-  </si>
-  <si>
     <t>@WarWorz</t>
   </si>
   <si>
@@ -617,12 +581,6 @@
     <t>@Bonzifer</t>
   </si>
   <si>
-    <t>@Giggi_A</t>
-  </si>
-  <si>
-    <t>@Madara_2912</t>
-  </si>
-  <si>
     <t>⭐️Marco⭐️</t>
   </si>
   <si>
@@ -647,69 +605,21 @@
     <t>@gambo84</t>
   </si>
   <si>
-    <t>@Balliver</t>
-  </si>
-  <si>
-    <t>ＡＲ♠️Ｆｅｄｅ</t>
-  </si>
-  <si>
-    <t>A R ♠️ FEDERICO</t>
-  </si>
-  <si>
     <t>ＡＲ♠️Ｇｅｅｎｏ</t>
   </si>
   <si>
-    <t>ＡＲ♠️Ｏｘｈａｔｒｅｓ</t>
-  </si>
-  <si>
-    <t>ᴀʀ♥️ᴍᴏɴɪᴀ</t>
-  </si>
-  <si>
-    <t>ＡＲ♥️Ｐｏｎｃｉｏ９９</t>
-  </si>
-  <si>
-    <t>ＡＲ♥️Ｓｔｅｆａｎｏ</t>
-  </si>
-  <si>
-    <t>ＡＲ♦️Ｂｏｓｏ</t>
-  </si>
-  <si>
-    <t>ＡＲ♦️ｏＢ❗️Ｒ</t>
-  </si>
-  <si>
-    <t>ＡＲ♦️Ｐｅｐｐｏｎｅ９１</t>
-  </si>
-  <si>
-    <t>ＡＲ❤️Ｔｅｆａｎｏｓ</t>
-  </si>
-  <si>
-    <t>AR❤️TORIAS</t>
-  </si>
-  <si>
     <t>@Alestrega22</t>
   </si>
   <si>
-    <t>@PepponeB91</t>
-  </si>
-  <si>
-    <t>ＡＲ♦️Ｌ．Ｌａｗｌｉｅｔ</t>
-  </si>
-  <si>
     <t>AR♦️MANGUSTA</t>
   </si>
   <si>
-    <t>ＡＲ❤️ＮｉｃｏＦｌａｓｈ</t>
-  </si>
-  <si>
     <t>fogu</t>
   </si>
   <si>
     <t>random guy</t>
   </si>
   <si>
-    <t>@PharmaShooter</t>
-  </si>
-  <si>
     <t>@mangusta_agile</t>
   </si>
   <si>
@@ -725,9 +635,6 @@
     <t>mastro olivo</t>
   </si>
   <si>
-    <t>Tori Feroci (Warlosing)</t>
-  </si>
-  <si>
     <t>KAIROS</t>
   </si>
   <si>
@@ -737,26 +644,71 @@
     <t>Zumpy</t>
   </si>
   <si>
-    <t>AR♣️STAR</t>
-  </si>
-  <si>
     <t>@orso_86</t>
   </si>
   <si>
     <t>@FabioZumpy77</t>
   </si>
   <si>
-    <t>Baby Rozza</t>
-  </si>
-  <si>
     <t>Si</t>
+  </si>
+  <si>
+    <t>Ａ Ｒ ♠️ ＦＥＤＥＲＩＣＯ</t>
+  </si>
+  <si>
+    <t>coraz</t>
+  </si>
+  <si>
+    <t>⚡️Įnđømînūsᴳᵒᵈ⚡️</t>
+  </si>
+  <si>
+    <t>⚡️妥Dɾąց๏ղ妥ᴳᵒᵈ⚡️</t>
+  </si>
+  <si>
+    <t>@MAIO34</t>
+  </si>
+  <si>
+    <t>@coraaaaz</t>
+  </si>
+  <si>
+    <t>@AR_Indominus</t>
+  </si>
+  <si>
+    <t>@AR_Drag0n</t>
+  </si>
+  <si>
+    <t>IL DISTRUTTORE</t>
+  </si>
+  <si>
+    <t>@doc0849</t>
+  </si>
+  <si>
+    <t>@gioee_e27</t>
+  </si>
+  <si>
+    <t>Warlosing</t>
+  </si>
+  <si>
+    <t>davide</t>
+  </si>
+  <si>
+    <t>ＡＲ♣️ＳＴＡＲ</t>
+  </si>
+  <si>
+    <t>Nervouse✨</t>
+  </si>
+  <si>
+    <t>@CR0LP0C</t>
+  </si>
+  <si>
+    <t>@Nervouseee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -890,12 +842,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1239,12 +1185,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1292,7 +1235,117 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1733,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1763,156 +1816,156 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>206</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>207</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1920,1532 +1973,1385 @@
         <v>122</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="B18" s="1" t="s">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="B19" s="1" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="B24" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="B28" s="1" t="s">
-        <v>215</v>
+        <v>48</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="B29" s="1" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>173</v>
+        <v>26</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>224</v>
+      <c r="A58" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>40</v>
+      <c r="A71" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>22</v>
+        <v>188</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>222</v>
+        <v>32</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>189</v>
+        <v>43</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>223</v>
+        <v>152</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>227</v>
+        <v>12</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>64</v>
+        <v>182</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>73</v>
+      <c r="A111" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3453,15 +3359,50 @@
     <sortCondition ref="C2:C118"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B96">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B49">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58:B61 B50:B56">
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:B56 B58:B61">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:B56 B58:B61">
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B106 B108:B110">
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B104:B106 B108:B110">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B103">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:B103">
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
+    <cfRule type="duplicateValues" dxfId="0" priority="-1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62BE6B4F-357C-433B-A4EB-A5CACFFA7FD4}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2704B309-1C22-4B48-87C7-101439DB86EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="224">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -702,6 +702,9 @@
   </si>
   <si>
     <t>@Nervouseee</t>
+  </si>
+  <si>
+    <t>✨いたChewingGum✨</t>
   </si>
 </sst>
 </file>
@@ -1235,57 +1238,7 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1786,7 +1739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1976,7 +1929,7 @@
         <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>205</v>
@@ -3351,6 +3304,17 @@
         <v>198</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B112" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3359,50 +3323,39 @@
     <sortCondition ref="C2:C118"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="21" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58:B61 B50:B56">
-    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B56 B58:B61">
     <cfRule type="duplicateValues" dxfId="11" priority="11"/>
     <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B56 B58:B61">
     <cfRule type="duplicateValues" dxfId="9" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B106 B108:B110">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B104:B106 B108:B110">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  <conditionalFormatting sqref="B58:B61 B50:B56">
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63:B103">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:B106 B108:B110">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B103">
     <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  <conditionalFormatting sqref="B104:B106 B108:B110">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="0" priority="-1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="458" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2704B309-1C22-4B48-87C7-101439DB86EF}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D3AF67-C4DB-45F7-A052-06F41CFC06E5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
@@ -650,9 +650,6 @@
     <t>@FabioZumpy77</t>
   </si>
   <si>
-    <t>Si</t>
-  </si>
-  <si>
     <t>Ａ Ｒ ♠️ ＦＥＤＥＲＩＣＯ</t>
   </si>
   <si>
@@ -705,6 +702,9 @@
   </si>
   <si>
     <t>✨いたChewingGum✨</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1778,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1792,7 +1792,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1806,7 +1806,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1814,13 +1814,13 @@
         <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1848,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1862,7 +1862,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1876,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1890,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1904,7 +1904,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1918,469 +1918,469 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>211</v>
+        <v>44</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>207</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -2394,12 +2394,12 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>209</v>
@@ -2408,919 +2408,919 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="B49" s="1" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>29</v>
+        <v>220</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>43</v>
+        <v>181</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>200</v>
+        <v>89</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="B112" s="1" t="s">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D118">
-    <sortCondition ref="C2:C118"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D112">
+    <sortCondition ref="C2:C112"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
     <cfRule type="duplicateValues" dxfId="16" priority="31"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0D3AF67-C4DB-45F7-A052-06F41CFC06E5}"/>
+  <xr:revisionPtr revIDLastSave="484" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A21FD45-08B6-4025-97C2-1036C1B994DE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="233">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -308,9 +308,6 @@
     <t>vinz</t>
   </si>
   <si>
-    <t>aleman(statale)</t>
-  </si>
-  <si>
     <t>ＡＲ♣️Ｃｉｃｃｉｏ</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t>ＡＲ♦️Ｅ＄</t>
   </si>
   <si>
-    <t>Ａｒ❤️Ｓａｍｕｅｌｅ</t>
-  </si>
-  <si>
     <t>ＡＲ♣️Ｒｉｃｃａｌｓｏ</t>
   </si>
   <si>
@@ -434,9 +428,6 @@
     <t>@BBCTR3</t>
   </si>
   <si>
-    <t>ＡＲ❤️Ｎｉｃｏ</t>
-  </si>
-  <si>
     <t>Luca01</t>
   </si>
   <si>
@@ -524,9 +515,6 @@
     <t>@Lucaser95</t>
   </si>
   <si>
-    <t>@Sgrillo97</t>
-  </si>
-  <si>
     <t>@superfede2</t>
   </si>
   <si>
@@ -581,9 +569,6 @@
     <t>@Bonzifer</t>
   </si>
   <si>
-    <t>⭐️Marco⭐️</t>
-  </si>
-  <si>
     <t>teo</t>
   </si>
   <si>
@@ -596,9 +581,6 @@
     <t>AR♠️MrDEATH</t>
   </si>
   <si>
-    <t>CcH LATINO™️</t>
-  </si>
-  <si>
     <t>prince</t>
   </si>
   <si>
@@ -617,21 +599,9 @@
     <t>fogu</t>
   </si>
   <si>
-    <t>random guy</t>
-  </si>
-  <si>
     <t>@mangusta_agile</t>
   </si>
   <si>
-    <t>@Davide438</t>
-  </si>
-  <si>
-    <t>@X_teo</t>
-  </si>
-  <si>
-    <t>Dog Rider</t>
-  </si>
-  <si>
     <t>mastro olivo</t>
   </si>
   <si>
@@ -656,12 +626,6 @@
     <t>coraz</t>
   </si>
   <si>
-    <t>⚡️Įnđømînūsᴳᵒᵈ⚡️</t>
-  </si>
-  <si>
-    <t>⚡️妥Dɾąց๏ղ妥ᴳᵒᵈ⚡️</t>
-  </si>
-  <si>
     <t>@MAIO34</t>
   </si>
   <si>
@@ -674,15 +638,9 @@
     <t>@AR_Drag0n</t>
   </si>
   <si>
-    <t>IL DISTRUTTORE</t>
-  </si>
-  <si>
     <t>@doc0849</t>
   </si>
   <si>
-    <t>@gioee_e27</t>
-  </si>
-  <si>
     <t>Warlosing</t>
   </si>
   <si>
@@ -704,7 +662,76 @@
     <t>✨いたChewingGum✨</t>
   </si>
   <si>
-    <t>No</t>
+    <t>⭐Marco⭐</t>
+  </si>
+  <si>
+    <t>aleama</t>
+  </si>
+  <si>
+    <t>Aleman(statale)</t>
+  </si>
+  <si>
+    <t>AR♠️BAC</t>
+  </si>
+  <si>
+    <t>AR♦️Peppone91</t>
+  </si>
+  <si>
+    <t>ＡＲ❤️ＮｉｃｏＦｌａｓｈ</t>
+  </si>
+  <si>
+    <t>Ａｒ❤Ｓａｍｕｅｌｅ</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+  </si>
+  <si>
+    <t>@M4nuel4617</t>
+  </si>
+  <si>
+    <t>@Aleama13</t>
+  </si>
+  <si>
+    <t>@BACWasTaken</t>
+  </si>
+  <si>
+    <t>@PepponeB91</t>
+  </si>
+  <si>
+    <t>@Arrow1407</t>
+  </si>
+  <si>
+    <t>⚡Įnđømînūsᴳᵒᵈ⚡</t>
+  </si>
+  <si>
+    <t>⚡妥Dɾąց๏ղ妥ᴳᵒᵈ⚡</t>
+  </si>
+  <si>
+    <t>@christian363</t>
+  </si>
+  <si>
+    <t>@Balliver</t>
+  </si>
+  <si>
+    <t>I Tori Feroci</t>
+  </si>
+  <si>
+    <t>AR♠️CcH LATINO™</t>
+  </si>
+  <si>
+    <t>AR♠️Fede</t>
+  </si>
+  <si>
+    <t>shinigami</t>
+  </si>
+  <si>
+    <t>two ciamela</t>
+  </si>
+  <si>
+    <t>@Giggi_A</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1265,427 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1739,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1769,937 +2216,940 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>190</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>184</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>73</v>
+        <v>205</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>3</v>
+        <v>226</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="B49" s="1" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>3</v>
+        <v>226</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>59</v>
+        <v>222</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>220</v>
+        <v>128</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>184</v>
+        <v>75</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2710,612 +3160,696 @@
         <v>60</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>163</v>
+        <v>26</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>49</v>
+        <v>160</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>218</v>
+        <v>136</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>72</v>
+        <v>225</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>11</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>219</v>
+        <v>91</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>29</v>
+        <v>183</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C112" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3323,39 +3857,119 @@
     <sortCondition ref="C2:C112"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+  <conditionalFormatting sqref="B43:B44 B2:B8 B10:B17 B20:B21 B23 B25 B40 B27 B35:B37 B29:B33">
+    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B56 B58:B61">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+  <conditionalFormatting sqref="B2:B18 B20:B23 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46">
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B58:B61 B50:B56">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  <conditionalFormatting sqref="B2:B18 B20:B23 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46">
+    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B103">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  <conditionalFormatting sqref="B47">
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B106 B108:B110">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  <conditionalFormatting sqref="B68:B69 B63:B65 B50:B51 B56:B60 B71 B53">
+    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B71">
+    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88:B93 B95 B72:B80 B82:B86">
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B71">
+    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B113 B96:B99 B116">
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B104:B105 B101">
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B100:B105">
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B106">
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B106">
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110">
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110">
+    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110">
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
+    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B114">
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B114">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B114">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64:B103">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+  <conditionalFormatting sqref="B117">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104:B106 B108:B110">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  <conditionalFormatting sqref="B96">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B118">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="484" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A21FD45-08B6-4025-97C2-1036C1B994DE}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAFF7500-468C-44C0-B846-F3A750A97F8F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -671,12 +671,6 @@
     <t>Aleman(statale)</t>
   </si>
   <si>
-    <t>AR♠️BAC</t>
-  </si>
-  <si>
-    <t>AR♦️Peppone91</t>
-  </si>
-  <si>
     <t>ＡＲ❤️ＮｉｃｏＦｌａｓｈ</t>
   </si>
   <si>
@@ -731,7 +725,13 @@
     <t>@Giggi_A</t>
   </si>
   <si>
-    <t>Si</t>
+    <t>ＡＲ♠️ＢＡＣ</t>
+  </si>
+  <si>
+    <t>ＡＲ♦️Ｐｅｐｐｏｎｅ９１</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1265,147 +1265,7 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2230,7 +2090,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>208</v>
@@ -2286,7 +2146,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>210</v>
@@ -2356,10 +2216,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2510,10 +2370,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2527,7 +2387,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2541,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2552,10 +2412,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2866,7 +2726,7 @@
         <v>197</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>232</v>
@@ -2880,7 +2740,7 @@
         <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>232</v>
@@ -2891,10 +2751,10 @@
         <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>232</v>
@@ -2905,10 +2765,10 @@
         <v>200</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>232</v>
@@ -2922,7 +2782,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>232</v>
@@ -2936,7 +2796,7 @@
         <v>34</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>232</v>
@@ -2950,7 +2810,7 @@
         <v>204</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>232</v>
@@ -2964,7 +2824,7 @@
         <v>145</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>232</v>
@@ -2978,7 +2838,7 @@
         <v>186</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>232</v>
@@ -2992,7 +2852,7 @@
         <v>141</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>232</v>
@@ -3006,7 +2866,7 @@
         <v>179</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>232</v>
@@ -3020,7 +2880,7 @@
         <v>68</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>232</v>
@@ -3034,7 +2894,7 @@
         <v>75</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>232</v>
@@ -3048,7 +2908,7 @@
         <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>232</v>
@@ -3062,7 +2922,7 @@
         <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>232</v>
@@ -3076,7 +2936,7 @@
         <v>67</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>232</v>
@@ -3090,7 +2950,7 @@
         <v>140</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>232</v>
@@ -3104,7 +2964,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>232</v>
@@ -3118,7 +2978,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>232</v>
@@ -3132,7 +2992,7 @@
         <v>22</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>232</v>
@@ -3146,7 +3006,7 @@
         <v>203</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>232</v>
@@ -3160,7 +3020,7 @@
         <v>60</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>232</v>
@@ -3174,7 +3034,7 @@
         <v>138</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>232</v>
@@ -3188,7 +3048,7 @@
         <v>149</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>232</v>
@@ -3202,7 +3062,7 @@
         <v>36</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>232</v>
@@ -3216,7 +3076,7 @@
         <v>187</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>232</v>
@@ -3230,7 +3090,7 @@
         <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>232</v>
@@ -3244,7 +3104,7 @@
         <v>150</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>232</v>
@@ -3258,7 +3118,7 @@
         <v>190</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>232</v>
@@ -3272,7 +3132,7 @@
         <v>133</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>232</v>
@@ -3286,7 +3146,7 @@
         <v>142</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>232</v>
@@ -3300,7 +3160,7 @@
         <v>64</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>232</v>
@@ -3314,7 +3174,7 @@
         <v>13</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>232</v>
@@ -3328,7 +3188,7 @@
         <v>191</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>232</v>
@@ -3342,7 +3202,7 @@
         <v>144</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>232</v>
@@ -3356,7 +3216,7 @@
         <v>151</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>232</v>
@@ -3370,7 +3230,7 @@
         <v>152</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>232</v>
@@ -3384,7 +3244,7 @@
         <v>153</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>232</v>
@@ -3392,13 +3252,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>232</v>
@@ -3412,7 +3272,7 @@
         <v>25</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>232</v>
@@ -3426,7 +3286,7 @@
         <v>136</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>232</v>
@@ -3440,7 +3300,7 @@
         <v>14</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>232</v>
@@ -3448,13 +3308,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>178</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>232</v>
@@ -3468,7 +3328,7 @@
         <v>11</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>232</v>
@@ -3482,7 +3342,7 @@
         <v>155</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>232</v>
@@ -3496,7 +3356,7 @@
         <v>57</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>232</v>
@@ -3510,7 +3370,7 @@
         <v>143</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>232</v>
@@ -3524,7 +3384,7 @@
         <v>192</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>232</v>
@@ -3535,7 +3395,7 @@
         <v>118</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>202</v>
@@ -3549,7 +3409,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>202</v>
@@ -3801,7 +3661,7 @@
         <v>99</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>202</v>
@@ -3826,10 +3686,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>202</v>
@@ -3857,119 +3717,93 @@
     <sortCondition ref="C2:C112"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="58" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B44 B2:B8 B10:B17 B20:B21 B23 B25 B40 B27 B35:B37 B29:B33">
-    <cfRule type="duplicateValues" dxfId="41" priority="40"/>
+  <conditionalFormatting sqref="B2:B11 B20:B22 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46 B13:B18">
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18 B20:B23 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18 B20:B23 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B44 B2:B8 B10:B11 B20:B21 B25 B40 B27 B35:B37 B29:B33 B13:B17">
+    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48:B71">
+    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B69 B63:B65 B50:B51 B56:B60 B71 B53">
-    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B71">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88:B93 B95 B72:B80 B82:B86">
-    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
+  <conditionalFormatting sqref="B96">
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
+  <conditionalFormatting sqref="B100:B105">
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:B71">
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
+  <conditionalFormatting sqref="B104:B105 B101">
+    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B106">
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B110">
+    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B112">
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 B96:B99 B116">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B104:B105 B101">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B100:B105">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B106">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B106">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAFF7500-468C-44C0-B846-F3A750A97F8F}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{039CCEBC-5086-4016-9980-4AC83D260EC0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -101,9 +101,6 @@
     <t>@domenico_9</t>
   </si>
   <si>
-    <t>dani_lanc</t>
-  </si>
-  <si>
     <t>simo99</t>
   </si>
   <si>
@@ -137,27 +134,18 @@
     <t>@niflash</t>
   </si>
   <si>
-    <t>Antonio96</t>
-  </si>
-  <si>
     <t>Frenk8</t>
   </si>
   <si>
     <t>Fabrizio</t>
   </si>
   <si>
-    <t>@totino96</t>
-  </si>
-  <si>
     <t>@Freenk8</t>
   </si>
   <si>
     <t>@Oneleggedjack</t>
   </si>
   <si>
-    <t>@asso_nr</t>
-  </si>
-  <si>
     <t>IceMan</t>
   </si>
   <si>
@@ -188,12 +176,6 @@
     <t>@User32418</t>
   </si>
   <si>
-    <t>@Augu05</t>
-  </si>
-  <si>
-    <t>Augu05</t>
-  </si>
-  <si>
     <t>@Cisco00001</t>
   </si>
   <si>
@@ -212,15 +194,9 @@
     <t>@The_Lore27</t>
   </si>
   <si>
-    <t>•fury™•</t>
-  </si>
-  <si>
     <t>Dino</t>
   </si>
   <si>
-    <t>@Manu2365</t>
-  </si>
-  <si>
     <t>@sunnering</t>
   </si>
   <si>
@@ -500,9 +476,6 @@
     <t>Teodoro⠀Mapuzzi</t>
   </si>
   <si>
-    <t>tiau</t>
-  </si>
-  <si>
     <t>@luca3689</t>
   </si>
   <si>
@@ -572,12 +545,6 @@
     <t>teo</t>
   </si>
   <si>
-    <t>arKaiba❤️Sparky</t>
-  </si>
-  <si>
-    <t>@sorridetemi</t>
-  </si>
-  <si>
     <t>AR♠️MrDEATH</t>
   </si>
   <si>
@@ -662,21 +629,12 @@
     <t>✨いたChewingGum✨</t>
   </si>
   <si>
-    <t>⭐Marco⭐</t>
-  </si>
-  <si>
     <t>aleama</t>
   </si>
   <si>
-    <t>Aleman(statale)</t>
-  </si>
-  <si>
     <t>ＡＲ❤️ＮｉｃｏＦｌａｓｈ</t>
   </si>
   <si>
-    <t>Ａｒ❤Ｓａｍｕｅｌｅ</t>
-  </si>
-  <si>
     <t>Arrow</t>
   </si>
   <si>
@@ -689,18 +647,9 @@
     <t>@BACWasTaken</t>
   </si>
   <si>
-    <t>@PepponeB91</t>
-  </si>
-  <si>
     <t>@Arrow1407</t>
   </si>
   <si>
-    <t>⚡Įnđømînūsᴳᵒᵈ⚡</t>
-  </si>
-  <si>
-    <t>⚡妥Dɾąց๏ղ妥ᴳᵒᵈ⚡</t>
-  </si>
-  <si>
     <t>@christian363</t>
   </si>
   <si>
@@ -710,15 +659,9 @@
     <t>I Tori Feroci</t>
   </si>
   <si>
-    <t>AR♠️CcH LATINO™</t>
-  </si>
-  <si>
     <t>AR♠️Fede</t>
   </si>
   <si>
-    <t>shinigami</t>
-  </si>
-  <si>
     <t>two ciamela</t>
   </si>
   <si>
@@ -728,10 +671,55 @@
     <t>ＡＲ♠️ＢＡＣ</t>
   </si>
   <si>
-    <t>ＡＲ♦️Ｐｅｐｐｏｎｅ９１</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>@Boso_7</t>
+  </si>
+  <si>
+    <t>ＡＲ♥️Ｓｔｅｆａｎｏ</t>
+  </si>
+  <si>
+    <t>ＡＲ♣️ΒΑΡΑΓΛΙΑ98</t>
+  </si>
+  <si>
+    <t>Ａｒ❤️Ｓａｍｕｅｌｅ</t>
+  </si>
+  <si>
+    <t>@tefanosss</t>
+  </si>
+  <si>
+    <t>⚡️妥Dɾąց๏ղ妥ᴳᵒᵈ⚡️</t>
+  </si>
+  <si>
+    <t>PIZZALILLO</t>
+  </si>
+  <si>
+    <t>CcH LATINO™️</t>
+  </si>
+  <si>
+    <t>Ignazio</t>
+  </si>
+  <si>
+    <t>⚡️Įnđømînūsᴳᵒᵈ⚡️</t>
+  </si>
+  <si>
+    <t>@kvaradona997</t>
+  </si>
+  <si>
+    <t>ＡＲ❤️Ｎｉｃｏ</t>
+  </si>
+  <si>
+    <t>~Nasty~</t>
+  </si>
+  <si>
+    <t>aleman(statale)</t>
+  </si>
+  <si>
+    <t>⭐️Marco⭐️</t>
+  </si>
+  <si>
+    <t>@Art_of_Leo</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -2046,12 +2034,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
     <col min="6" max="6" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2071,455 +2059,455 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>59</v>
+        <v>213</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>218</v>
+        <v>148</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>231</v>
+        <v>124</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>212</v>
+        <v>81</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>213</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>219</v>
+        <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2527,1189 +2515,1147 @@
         <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>220</v>
+        <v>84</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>222</v>
+        <v>12</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>15</v>
+        <v>222</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>14</v>
+        <v>220</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>201</v>
+        <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>8</v>
+        <v>225</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>227</v>
+        <v>72</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{039CCEBC-5086-4016-9980-4AC83D260EC0}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6C94A1-CEF5-4419-8372-931CF1D70A23}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="228">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Dino</t>
   </si>
   <si>
-    <t>@sunnering</t>
-  </si>
-  <si>
     <t>DOCCC</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t>@Chris_0773</t>
   </si>
   <si>
-    <t>@Zumo0o</t>
-  </si>
-  <si>
     <t>@ralfone01</t>
   </si>
   <si>
@@ -395,9 +389,6 @@
     <t>@Fox_0265</t>
   </si>
   <si>
-    <t>@ZuMo0o</t>
-  </si>
-  <si>
     <t>@MerMet92</t>
   </si>
   <si>
@@ -527,9 +518,6 @@
     <t>@Don_Michele_Royale</t>
   </si>
   <si>
-    <t>@srd_rce</t>
-  </si>
-  <si>
     <t>@Frittuuu</t>
   </si>
   <si>
@@ -720,6 +708,15 @@
   </si>
   <si>
     <t>Si</t>
+  </si>
+  <si>
+    <t>@ZuMoOoO</t>
+  </si>
+  <si>
+    <t>@srdrce</t>
+  </si>
+  <si>
+    <t>@WildTech_Project</t>
   </si>
 </sst>
 </file>
@@ -2064,16 +2061,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2081,41 +2078,41 @@
         <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2129,35 +2126,35 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2165,125 +2162,125 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2297,35 +2294,35 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2333,13 +2330,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2353,105 +2350,105 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2465,63 +2462,63 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2535,35 +2532,35 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -2577,7 +2574,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2591,7 +2588,7 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2605,7 +2602,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -2619,63 +2616,63 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -2689,7 +2686,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -2703,119 +2700,119 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -2826,94 +2823,94 @@
         <v>13</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -2924,52 +2921,52 @@
         <v>37</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -2980,24 +2977,24 @@
         <v>14</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -3008,10 +3005,10 @@
         <v>9</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -3022,24 +3019,24 @@
         <v>51</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -3050,136 +3047,136 @@
         <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -3190,24 +3187,24 @@
         <v>34</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -3218,24 +3215,24 @@
         <v>48</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -3246,108 +3243,108 @@
         <v>11</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -3355,111 +3352,111 @@
         <v>45</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -3467,13 +3464,13 @@
         <v>32</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -3484,10 +3481,10 @@
         <v>27</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -3495,27 +3492,27 @@
         <v>28</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -3526,108 +3523,108 @@
         <v>30</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="D111" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -3635,27 +3632,27 @@
         <v>19</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6C94A1-CEF5-4419-8372-931CF1D70A23}"/>
+  <xr:revisionPtr revIDLastSave="597" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F22F756E-8611-4232-820B-67C305831519}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="247">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -215,12 +215,6 @@
     <t>Beéle</t>
   </si>
   <si>
-    <t>DAI HOPP</t>
-  </si>
-  <si>
-    <t>@andrea_cop</t>
-  </si>
-  <si>
     <t>@simoscalora</t>
   </si>
   <si>
@@ -551,9 +545,6 @@
     <t>AR♦️MANGUSTA</t>
   </si>
   <si>
-    <t>fogu</t>
-  </si>
-  <si>
     <t>@mangusta_agile</t>
   </si>
   <si>
@@ -647,9 +638,6 @@
     <t>I Tori Feroci</t>
   </si>
   <si>
-    <t>AR♠️Fede</t>
-  </si>
-  <si>
     <t>two ciamela</t>
   </si>
   <si>
@@ -665,33 +653,15 @@
     <t>ＡＲ♥️Ｓｔｅｆａｎｏ</t>
   </si>
   <si>
-    <t>ＡＲ♣️ΒΑΡΑΓΛΙΑ98</t>
-  </si>
-  <si>
-    <t>Ａｒ❤️Ｓａｍｕｅｌｅ</t>
-  </si>
-  <si>
     <t>@tefanosss</t>
   </si>
   <si>
-    <t>⚡️妥Dɾąց๏ղ妥ᴳᵒᵈ⚡️</t>
-  </si>
-  <si>
     <t>PIZZALILLO</t>
   </si>
   <si>
     <t>CcH LATINO™️</t>
   </si>
   <si>
-    <t>Ignazio</t>
-  </si>
-  <si>
-    <t>⚡️Įnđømînūsᴳᵒᵈ⚡️</t>
-  </si>
-  <si>
-    <t>@kvaradona997</t>
-  </si>
-  <si>
     <t>ＡＲ❤️Ｎｉｃｏ</t>
   </si>
   <si>
@@ -701,9 +671,6 @@
     <t>aleman(statale)</t>
   </si>
   <si>
-    <t>⭐️Marco⭐️</t>
-  </si>
-  <si>
     <t>@Art_of_Leo</t>
   </si>
   <si>
@@ -717,6 +684,96 @@
   </si>
   <si>
     <t>@WildTech_Project</t>
+  </si>
+  <si>
+    <t>Ａｒ❤Ｓａｍｕｅｌｅ</t>
+  </si>
+  <si>
+    <t>ＡＲ♠️Ｍｉｃｈａｅｌ</t>
+  </si>
+  <si>
+    <t>⭐Marco⭐</t>
+  </si>
+  <si>
+    <t>ＡＲ❤️Ｔｅｆａｎｏｓ</t>
+  </si>
+  <si>
+    <t>ＡＲ♠️Ｆｅｄｅ</t>
+  </si>
+  <si>
+    <t>ＡＲ♦️Ｂｏｓｏ</t>
+  </si>
+  <si>
+    <t>@Micro723</t>
+  </si>
+  <si>
+    <t>⚡妥Dɾąց๏ղ妥ᴳᵒᵈ⚡</t>
+  </si>
+  <si>
+    <t>Ale</t>
+  </si>
+  <si>
+    <t>Just_Dodo</t>
+  </si>
+  <si>
+    <t>Vinny</t>
+  </si>
+  <si>
+    <t>Antonio96</t>
+  </si>
+  <si>
+    <t>⚡Įnđømînūsᴳᵒᵈ⚡</t>
+  </si>
+  <si>
+    <t>ＡＲ♠️Ｓｍａｎｎａ</t>
+  </si>
+  <si>
+    <t>@cris_0000001</t>
+  </si>
+  <si>
+    <t>@edoogrigo</t>
+  </si>
+  <si>
+    <t>@dragoon_enjoyer</t>
+  </si>
+  <si>
+    <t>@totino96</t>
+  </si>
+  <si>
+    <t>ＡＲ❤️ＢａｂｙＳｔｅ</t>
+  </si>
+  <si>
+    <t>Quizzz</t>
+  </si>
+  <si>
+    <t>shinigami</t>
+  </si>
+  <si>
+    <t>ＡＲ♥️Ｐｏｎｃｉｏ９９</t>
+  </si>
+  <si>
+    <t>•fury™•</t>
+  </si>
+  <si>
+    <t>Augu05</t>
+  </si>
+  <si>
+    <t>@Manu2365</t>
+  </si>
+  <si>
+    <t>@Augu05</t>
+  </si>
+  <si>
+    <t>tiau</t>
+  </si>
+  <si>
+    <t>DADDA</t>
+  </si>
+  <si>
+    <t>@danielylo</t>
+  </si>
+  <si>
+    <t>Baby Rozza</t>
   </si>
 </sst>
 </file>
@@ -1200,9 +1257,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1310,297 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="74">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2031,11 +2381,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
@@ -2061,422 +2411,422 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>224</v>
+      <c r="D2" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>224</v>
+      <c r="D3" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>224</v>
+      <c r="D4" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>224</v>
+      <c r="D5" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>224</v>
+      <c r="D6" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>224</v>
+      <c r="D7" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>224</v>
+      <c r="D8" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>224</v>
+      <c r="D9" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>224</v>
+      <c r="D10" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>224</v>
+      <c r="D11" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>224</v>
+      <c r="D12" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>224</v>
+      <c r="D13" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>224</v>
+      <c r="D14" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>224</v>
+      <c r="D15" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>224</v>
+      <c r="D16" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>224</v>
+      <c r="D17" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>224</v>
+      <c r="D18" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>224</v>
+      <c r="D19" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>224</v>
+      <c r="D20" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>224</v>
+      <c r="D21" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>224</v>
+      <c r="D22" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>224</v>
+      <c r="D23" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>224</v>
+      <c r="D24" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>219</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>224</v>
+      <c r="D25" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>224</v>
+      <c r="D26" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>224</v>
+      <c r="D27" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>224</v>
+      <c r="D28" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>224</v>
+      <c r="D29" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>224</v>
+      <c r="D30" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>224</v>
+      <c r="D31" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -2489,988 +2839,988 @@
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>224</v>
+      <c r="D32" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>224</v>
+      <c r="D33" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>224</v>
+      <c r="D34" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>224</v>
+      <c r="D35" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>224</v>
+      <c r="D36" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>224</v>
+      <c r="D37" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>224</v>
+      <c r="D38" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>224</v>
+      <c r="D39" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>224</v>
+      <c r="D40" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>224</v>
+      <c r="D41" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>224</v>
+      <c r="D42" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>224</v>
+      <c r="D43" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>224</v>
+      <c r="D44" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>120</v>
+        <v>222</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>224</v>
+      <c r="D45" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>33</v>
+        <v>191</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>224</v>
+      <c r="D46" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>224</v>
+      <c r="D47" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>224</v>
+      <c r="D48" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>224</v>
+      <c r="D49" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>224</v>
+      <c r="D50" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>119</v>
+        <v>202</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>227</v>
+        <v>151</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>186</v>
+        <v>12</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>217</v>
+        <v>31</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>219</v>
+        <v>141</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -3478,181 +3828,363 @@
         <v>28</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>143</v>
+        <v>207</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>221</v>
+        <v>55</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>222</v>
+        <v>49</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>224</v>
+        <v>184</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3660,93 +4192,93 @@
     <sortCondition ref="C2:C112"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="44" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B11 B20:B22 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46 B13:B18">
-    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43:B44 B2:B8 B10:B11 B20:B21 B25 B40 B27 B35:B37 B29:B33 B13:B17">
-    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B71">
-    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B69 B63:B65 B50:B51 B56:B60 B71 B53">
-    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88:B93 B95 B72:B80 B82:B86">
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100:B105">
-    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104:B105 B101">
-    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 B96:B99 B116">
-    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="597" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F22F756E-8611-4232-820B-67C305831519}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8AB7859-20B1-4C4F-A277-5DDC081411C7}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -674,9 +674,6 @@
     <t>@Art_of_Leo</t>
   </si>
   <si>
-    <t>Si</t>
-  </si>
-  <si>
     <t>@ZuMoOoO</t>
   </si>
   <si>
@@ -774,6 +771,9 @@
   </si>
   <si>
     <t>Baby Rozza</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1257,12 +1257,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1310,297 +1307,7 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="74">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2419,8 +2126,8 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>213</v>
+      <c r="D2" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2433,8 +2140,8 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>213</v>
+      <c r="D3" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2447,8 +2154,8 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>213</v>
+      <c r="D4" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2461,8 +2168,8 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>213</v>
+      <c r="D5" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2475,8 +2182,8 @@
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>213</v>
+      <c r="D6" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -2489,8 +2196,8 @@
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>213</v>
+      <c r="D7" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2503,8 +2210,8 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>213</v>
+      <c r="D8" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2517,13 +2224,13 @@
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>213</v>
+      <c r="D9" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>70</v>
@@ -2531,8 +2238,8 @@
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>213</v>
+      <c r="D10" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2545,8 +2252,8 @@
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>213</v>
+      <c r="D11" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2559,8 +2266,8 @@
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>213</v>
+      <c r="D12" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2573,8 +2280,8 @@
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>213</v>
+      <c r="D13" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -2587,8 +2294,8 @@
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>213</v>
+      <c r="D14" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2596,13 +2303,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>213</v>
+      <c r="D15" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -2615,22 +2322,22 @@
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>213</v>
+      <c r="D16" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>213</v>
+      <c r="D17" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2643,8 +2350,8 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>213</v>
+      <c r="D18" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2657,8 +2364,8 @@
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>213</v>
+      <c r="D19" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2671,8 +2378,8 @@
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>213</v>
+      <c r="D20" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2685,8 +2392,8 @@
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>213</v>
+      <c r="D21" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2699,8 +2406,8 @@
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>213</v>
+      <c r="D22" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2713,8 +2420,8 @@
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>213</v>
+      <c r="D23" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2727,8 +2434,8 @@
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>213</v>
+      <c r="D24" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2736,13 +2443,13 @@
         <v>19</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>213</v>
+      <c r="D25" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2755,8 +2462,8 @@
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>213</v>
+      <c r="D26" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2769,8 +2476,8 @@
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>213</v>
+      <c r="D27" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2783,8 +2490,8 @@
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>213</v>
+      <c r="D28" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2797,8 +2504,8 @@
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>213</v>
+      <c r="D29" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2811,8 +2518,8 @@
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>213</v>
+      <c r="D30" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -2825,8 +2532,8 @@
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>213</v>
+      <c r="D31" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -2839,8 +2546,8 @@
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>213</v>
+      <c r="D32" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -2853,8 +2560,8 @@
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>213</v>
+      <c r="D33" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2867,8 +2574,8 @@
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>213</v>
+      <c r="D34" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2881,8 +2588,8 @@
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>213</v>
+      <c r="D35" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2895,8 +2602,8 @@
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>213</v>
+      <c r="D36" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2909,8 +2616,8 @@
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>213</v>
+      <c r="D37" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -2923,8 +2630,8 @@
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>213</v>
+      <c r="D38" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2937,8 +2644,8 @@
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>213</v>
+      <c r="D39" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2951,8 +2658,8 @@
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>213</v>
+      <c r="D40" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -2960,13 +2667,13 @@
         <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>213</v>
+      <c r="D41" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -2974,13 +2681,13 @@
         <v>88</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>213</v>
+      <c r="D42" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -2993,8 +2700,8 @@
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>213</v>
+      <c r="D43" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -3007,8 +2714,8 @@
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>213</v>
+      <c r="D44" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -3016,13 +2723,13 @@
         <v>204</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>213</v>
+      <c r="D45" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -3035,8 +2742,8 @@
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>213</v>
+      <c r="D46" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -3049,8 +2756,8 @@
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>213</v>
+      <c r="D47" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -3063,8 +2770,8 @@
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>213</v>
+      <c r="D48" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -3077,8 +2784,8 @@
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>213</v>
+      <c r="D49" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -3091,8 +2798,8 @@
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>213</v>
+      <c r="D50" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -3105,8 +2812,8 @@
       <c r="C51" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>213</v>
+      <c r="D51" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -3119,8 +2826,8 @@
       <c r="C52" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>213</v>
+      <c r="D52" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -3133,8 +2840,8 @@
       <c r="C53" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>213</v>
+      <c r="D53" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -3142,27 +2849,27 @@
         <v>182</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>213</v>
+      <c r="D54" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>213</v>
+      <c r="D55" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -3175,8 +2882,8 @@
       <c r="C56" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>213</v>
+      <c r="D56" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -3189,8 +2896,8 @@
       <c r="C57" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>213</v>
+      <c r="D57" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -3203,36 +2910,36 @@
       <c r="C58" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>213</v>
+      <c r="D58" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>213</v>
+      <c r="D59" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>213</v>
+      <c r="D60" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -3245,13 +2952,13 @@
       <c r="C61" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>213</v>
+      <c r="D61" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>59</v>
@@ -3259,8 +2966,8 @@
       <c r="C62" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>213</v>
+      <c r="D62" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -3273,8 +2980,8 @@
       <c r="C63" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>213</v>
+      <c r="D63" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -3287,8 +2994,8 @@
       <c r="C64" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>213</v>
+      <c r="D64" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -3301,8 +3008,8 @@
       <c r="C65" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>213</v>
+      <c r="D65" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -3315,8 +3022,8 @@
       <c r="C66" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>213</v>
+      <c r="D66" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -3329,8 +3036,8 @@
       <c r="C67" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>213</v>
+      <c r="D67" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -3343,8 +3050,8 @@
       <c r="C68" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>213</v>
+      <c r="D68" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -3357,8 +3064,8 @@
       <c r="C69" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>213</v>
+      <c r="D69" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -3371,8 +3078,8 @@
       <c r="C70" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>213</v>
+      <c r="D70" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -3385,8 +3092,8 @@
       <c r="C71" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>213</v>
+      <c r="D71" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -3399,8 +3106,8 @@
       <c r="C72" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>213</v>
+      <c r="D72" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -3413,8 +3120,8 @@
       <c r="C73" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>213</v>
+      <c r="D73" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -3427,22 +3134,22 @@
       <c r="C74" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>213</v>
+      <c r="D74" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>213</v>
+      <c r="D75" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -3455,8 +3162,8 @@
       <c r="C76" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>213</v>
+      <c r="D76" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -3469,8 +3176,8 @@
       <c r="C77" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>213</v>
+      <c r="D77" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -3478,18 +3185,18 @@
         <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>213</v>
+      <c r="D78" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>53</v>
@@ -3497,8 +3204,8 @@
       <c r="C79" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>213</v>
+      <c r="D79" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -3511,8 +3218,8 @@
       <c r="C80" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>213</v>
+      <c r="D80" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -3525,13 +3232,13 @@
       <c r="C81" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>213</v>
+      <c r="D81" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>136</v>
@@ -3539,8 +3246,8 @@
       <c r="C82" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>213</v>
+      <c r="D82" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -3553,8 +3260,8 @@
       <c r="C83" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>213</v>
+      <c r="D83" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -3567,8 +3274,8 @@
       <c r="C84" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>213</v>
+      <c r="D84" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -3581,8 +3288,8 @@
       <c r="C85" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>213</v>
+      <c r="D85" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -3595,8 +3302,8 @@
       <c r="C86" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>213</v>
+      <c r="D86" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -3609,8 +3316,8 @@
       <c r="C87" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>213</v>
+      <c r="D87" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -3623,8 +3330,8 @@
       <c r="C88" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>213</v>
+      <c r="D88" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -3637,8 +3344,8 @@
       <c r="C89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>213</v>
+      <c r="D89" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -3651,8 +3358,8 @@
       <c r="C90" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>213</v>
+      <c r="D90" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -3665,8 +3372,8 @@
       <c r="C91" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>213</v>
+      <c r="D91" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -3679,8 +3386,8 @@
       <c r="C92" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>213</v>
+      <c r="D92" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -3693,22 +3400,22 @@
       <c r="C93" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>213</v>
+      <c r="D93" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>213</v>
+      <c r="D94" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -3721,8 +3428,8 @@
       <c r="C95" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>213</v>
+      <c r="D95" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -3735,8 +3442,8 @@
       <c r="C96" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>213</v>
+      <c r="D96" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -3749,8 +3456,8 @@
       <c r="C97" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>213</v>
+      <c r="D97" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -3763,8 +3470,8 @@
       <c r="C98" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>213</v>
+      <c r="D98" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -3777,8 +3484,8 @@
       <c r="C99" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>213</v>
+      <c r="D99" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -3786,13 +3493,13 @@
         <v>206</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>213</v>
+      <c r="D100" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -3800,13 +3507,13 @@
         <v>196</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>213</v>
+      <c r="D101" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -3819,8 +3526,8 @@
       <c r="C102" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>213</v>
+      <c r="D102" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -3833,8 +3540,8 @@
       <c r="C103" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>213</v>
+      <c r="D103" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -3847,8 +3554,8 @@
       <c r="C104" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>213</v>
+      <c r="D104" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -3856,13 +3563,13 @@
         <v>88</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>213</v>
+      <c r="D105" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -3875,8 +3582,8 @@
       <c r="C106" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>213</v>
+      <c r="D106" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -3884,13 +3591,13 @@
         <v>206</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>213</v>
+      <c r="D107" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -3903,22 +3610,22 @@
       <c r="C108" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>213</v>
+      <c r="D108" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>213</v>
+      <c r="D109" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -3931,22 +3638,22 @@
       <c r="C110" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>213</v>
+      <c r="D110" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>213</v>
+      <c r="D111" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -3959,8 +3666,8 @@
       <c r="C112" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>213</v>
+      <c r="D112" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -3973,8 +3680,8 @@
       <c r="C113" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>213</v>
+      <c r="D113" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -3987,8 +3694,8 @@
       <c r="C114" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>213</v>
+      <c r="D114" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -4001,8 +3708,8 @@
       <c r="C115" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>213</v>
+      <c r="D115" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -4015,8 +3722,8 @@
       <c r="C116" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>213</v>
+      <c r="D116" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -4029,8 +3736,8 @@
       <c r="C117" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>213</v>
+      <c r="D117" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -4041,10 +3748,10 @@
         <v>79</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -4055,10 +3762,10 @@
         <v>173</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -4069,10 +3776,10 @@
         <v>125</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -4083,10 +3790,10 @@
         <v>139</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -4097,10 +3804,10 @@
         <v>163</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -4108,27 +3815,27 @@
         <v>117</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>213</v>
+      <c r="D124" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -4139,10 +3846,10 @@
         <v>174</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -4153,10 +3860,10 @@
         <v>132</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -4167,10 +3874,10 @@
         <v>208</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -4181,10 +3888,10 @@
         <v>120</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -4192,93 +3899,93 @@
     <sortCondition ref="C2:C112"/>
   </sortState>
   <conditionalFormatting sqref="A137:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="73" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B11 B20:B22 B25:B27 B35:B38 B40:B41 B29:B33 B43:B46 B13:B18">
-    <cfRule type="duplicateValues" dxfId="72" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="69" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="68" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43:B44 B2:B8 B10:B11 B20:B21 B25 B40 B27 B35:B37 B29:B33 B13:B17">
-    <cfRule type="duplicateValues" dxfId="67" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="66" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B71">
-    <cfRule type="duplicateValues" dxfId="65" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B69 B63:B65 B50:B51 B56:B60 B71 B53">
-    <cfRule type="duplicateValues" dxfId="63" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="62" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88:B93 B95 B72:B80 B82:B86">
-    <cfRule type="duplicateValues" dxfId="60" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="59" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100:B105">
-    <cfRule type="duplicateValues" dxfId="58" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104:B105 B101">
-    <cfRule type="duplicateValues" dxfId="57" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
-    <cfRule type="duplicateValues" dxfId="56" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="53" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="49" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="45" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113 B96:B99 B116">
-    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="41" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="37" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="599" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8AB7859-20B1-4C4F-A277-5DDC081411C7}"/>
+  <xr:revisionPtr revIDLastSave="622" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCEC5905-033A-4178-9E74-B707C0EE938F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="258">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -95,12 +95,6 @@
     <t>@MarcoP_PM</t>
   </si>
   <si>
-    <t>Domenico</t>
-  </si>
-  <si>
-    <t>@domenico_9</t>
-  </si>
-  <si>
     <t>simo99</t>
   </si>
   <si>
@@ -431,9 +425,6 @@
     <t>Pinguino</t>
   </si>
   <si>
-    <t>ＡＲ♣️Ｓｕｎｄｒｉｐｓ</t>
-  </si>
-  <si>
     <t>Bombazza</t>
   </si>
   <si>
@@ -554,21 +545,6 @@
     <t>KAIROS</t>
   </si>
   <si>
-    <t>orso86</t>
-  </si>
-  <si>
-    <t>Zumpy</t>
-  </si>
-  <si>
-    <t>@orso_86</t>
-  </si>
-  <si>
-    <t>@FabioZumpy77</t>
-  </si>
-  <si>
-    <t>Ａ Ｒ ♠️ ＦＥＤＥＲＩＣＯ</t>
-  </si>
-  <si>
     <t>coraz</t>
   </si>
   <si>
@@ -587,9 +563,6 @@
     <t>@doc0849</t>
   </si>
   <si>
-    <t>Warlosing</t>
-  </si>
-  <si>
     <t>davide</t>
   </si>
   <si>
@@ -659,12 +632,6 @@
     <t>PIZZALILLO</t>
   </si>
   <si>
-    <t>CcH LATINO™️</t>
-  </si>
-  <si>
-    <t>ＡＲ❤️Ｎｉｃｏ</t>
-  </si>
-  <si>
     <t>~Nasty~</t>
   </si>
   <si>
@@ -686,9 +653,6 @@
     <t>Ａｒ❤Ｓａｍｕｅｌｅ</t>
   </si>
   <si>
-    <t>ＡＲ♠️Ｍｉｃｈａｅｌ</t>
-  </si>
-  <si>
     <t>⭐Marco⭐</t>
   </si>
   <si>
@@ -701,39 +665,21 @@
     <t>ＡＲ♦️Ｂｏｓｏ</t>
   </si>
   <si>
-    <t>@Micro723</t>
-  </si>
-  <si>
     <t>⚡妥Dɾąց๏ղ妥ᴳᵒᵈ⚡</t>
   </si>
   <si>
-    <t>Ale</t>
-  </si>
-  <si>
     <t>Just_Dodo</t>
   </si>
   <si>
-    <t>Vinny</t>
-  </si>
-  <si>
     <t>Antonio96</t>
   </si>
   <si>
     <t>⚡Įnđømînūsᴳᵒᵈ⚡</t>
   </si>
   <si>
-    <t>ＡＲ♠️Ｓｍａｎｎａ</t>
-  </si>
-  <si>
-    <t>@cris_0000001</t>
-  </si>
-  <si>
     <t>@edoogrigo</t>
   </si>
   <si>
-    <t>@dragoon_enjoyer</t>
-  </si>
-  <si>
     <t>@totino96</t>
   </si>
   <si>
@@ -749,31 +695,118 @@
     <t>ＡＲ♥️Ｐｏｎｃｉｏ９９</t>
   </si>
   <si>
-    <t>•fury™•</t>
-  </si>
-  <si>
-    <t>Augu05</t>
-  </si>
-  <si>
-    <t>@Manu2365</t>
-  </si>
-  <si>
-    <t>@Augu05</t>
-  </si>
-  <si>
     <t>tiau</t>
   </si>
   <si>
-    <t>DADDA</t>
-  </si>
-  <si>
-    <t>@danielylo</t>
-  </si>
-  <si>
-    <t>Baby Rozza</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>@wa1n8</t>
+  </si>
+  <si>
+    <t>ＡＲ♦️ＭｉＳＴｉＺｉＯ☮️</t>
+  </si>
+  <si>
+    <t>Sønサル•D•Lůffy</t>
+  </si>
+  <si>
+    <t>A R ♠️ FEDERICO</t>
+  </si>
+  <si>
+    <t>AR❤️TORIAS</t>
+  </si>
+  <si>
+    <t>ＢＲ♠️ＤｏＮ</t>
+  </si>
+  <si>
+    <t>@PepponeB91</t>
+  </si>
+  <si>
+    <t>ＡＲ♦️ｏＢ❗Ｒ</t>
+  </si>
+  <si>
+    <t>ＡＲ♠️＠ｌｅｍａｎ</t>
+  </si>
+  <si>
+    <t>AR❤️Nico</t>
+  </si>
+  <si>
+    <t>ＡＲ♦️Ｐｅｐｐｏｎｅ９１</t>
+  </si>
+  <si>
+    <t>Thor⚡️</t>
+  </si>
+  <si>
+    <t>『2E』☣️Tøxîç☣️||</t>
+  </si>
+  <si>
+    <t>AR♣️Sundrips</t>
+  </si>
+  <si>
+    <t>arKaiba❤️Sparky</t>
+  </si>
+  <si>
+    <t>CINISELLO.4.20</t>
+  </si>
+  <si>
+    <t>DAI HOPP</t>
+  </si>
+  <si>
+    <t>frankye73</t>
+  </si>
+  <si>
+    <t>MARCHIO</t>
+  </si>
+  <si>
+    <t>Presidente</t>
+  </si>
+  <si>
+    <t>Uchiha Madara</t>
+  </si>
+  <si>
+    <t>lord Tony</t>
+  </si>
+  <si>
+    <t>fogu</t>
+  </si>
+  <si>
+    <t>AR♠️CcH LATINOTM</t>
+  </si>
+  <si>
+    <t>ＡＲ♣️ＲｏｚｚｏＤａＳｏｓａ</t>
+  </si>
+  <si>
+    <t>Cuba❤️Eren</t>
+  </si>
+  <si>
+    <t>@sorridetemi</t>
+  </si>
+  <si>
+    <t>@cinisello_420</t>
+  </si>
+  <si>
+    <t>@andrea_cop</t>
+  </si>
+  <si>
+    <t>@frankye73</t>
+  </si>
+  <si>
+    <t>@Marchio04</t>
+  </si>
+  <si>
+    <t>@PresidenteAP</t>
+  </si>
+  <si>
+    <t>@Madara_2912</t>
+  </si>
+  <si>
+    <t>@T0N1003</t>
+  </si>
+  <si>
+    <t>@cvbalibre</t>
+  </si>
+  <si>
+    <t>Dog Rider</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -2088,11 +2121,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
@@ -2113,558 +2146,558 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>104</v>
+        <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>208</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>212</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>44</v>
+        <v>207</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>219</v>
@@ -2673,63 +2706,63 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -2737,391 +2770,391 @@
         <v>195</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>225</v>
+        <v>128</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>213</v>
+        <v>5</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>10</v>
+        <v>214</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -3129,769 +3162,892 @@
         <v>61</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>36</v>
+        <v>188</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>214</v>
+        <v>12</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>8</v>
+        <v>127</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>57</v>
+        <v>190</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>135</v>
+        <v>212</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="B97" s="1" t="s">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C99" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C102" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>156</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>239</v>
+        <v>134</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>243</v>
+        <v>118</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>132</v>
+        <v>243</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>246</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ee4892a2dd36b84/Desktop/Link-clan/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="622" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCEC5905-033A-4178-9E74-B707C0EE938F}"/>
+  <xr:revisionPtr revIDLastSave="630" documentId="13_ncr:1_{9FCDD52C-4DCE-46C4-BB20-7F2264BA0663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B354F371-E045-4228-8881-4FCE9621B82B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FECCDA54-7594-4EB7-ABFB-2C408C6461DD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="262">
   <si>
     <t>TagTelegram</t>
   </si>
@@ -416,9 +416,6 @@
     <t>ＡＲ❤️Ｄａｒｋ Ａｎｇｅｌ</t>
   </si>
   <si>
-    <t>KOKODEWA</t>
-  </si>
-  <si>
     <t>vincy</t>
   </si>
   <si>
@@ -482,9 +479,6 @@
     <t>@An_dr3a514</t>
   </si>
   <si>
-    <t>@Anti47394</t>
-  </si>
-  <si>
     <t>@VincyR70</t>
   </si>
   <si>
@@ -807,6 +801,24 @@
   </si>
   <si>
     <t>Si</t>
+  </si>
+  <si>
+    <t>Augu05</t>
+  </si>
+  <si>
+    <t>Lucalby</t>
+  </si>
+  <si>
+    <t>Domenico</t>
+  </si>
+  <si>
+    <t>@augu05</t>
+  </si>
+  <si>
+    <t>@Lucalby</t>
+  </si>
+  <si>
+    <t>@domenico_9</t>
   </si>
 </sst>
 </file>
@@ -2121,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE2B0F9-AC31-464B-B046-53CB033C8615}">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -2154,13 +2166,13 @@
         <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2174,21 +2186,21 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2202,7 +2214,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2210,13 +2222,13 @@
         <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -2230,21 +2242,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2258,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -2272,7 +2284,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2286,12 +2298,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>117</v>
@@ -2300,7 +2312,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2314,21 +2326,21 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2342,7 +2354,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -2356,21 +2368,21 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2384,7 +2396,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2392,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2412,35 +2424,35 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2448,13 +2460,13 @@
         <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2468,7 +2480,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2482,7 +2494,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2496,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2510,7 +2522,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2518,13 +2530,13 @@
         <v>87</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -2532,13 +2544,13 @@
         <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -2552,7 +2564,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -2566,12 +2578,12 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>68</v>
@@ -2580,7 +2592,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -2594,7 +2606,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2608,7 +2620,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2622,21 +2634,21 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -2644,27 +2656,27 @@
         <v>7</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -2672,55 +2684,55 @@
         <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -2734,7 +2746,7 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -2742,41 +2754,41 @@
         <v>19</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -2790,12 +2802,12 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>52</v>
@@ -2804,7 +2816,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -2812,1242 +2824,1270 @@
         <v>86</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>189</v>
+        <v>247</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>202</v>
+        <v>48</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>23</v>
+        <v>250</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>22</v>
+        <v>238</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>26</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>14</v>
+        <v>239</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>132</v>
+        <v>242</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>201</v>
+        <v>10</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>30</v>
+        <v>191</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="B97" s="1" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>32</v>
+        <v>208</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>57</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>238</v>
+        <v>129</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>239</v>
+        <v>14</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>217</v>
+        <v>135</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>197</v>
+        <v>30</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>10</v>
+        <v>219</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>9</v>
+        <v>230</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>255</v>
+        <v>93</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>246</v>
+        <v>69</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B139" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
